--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5425" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5425" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1380,6 +1380,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -7719,7 +7723,7 @@
         <v>435</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7728,10 +7732,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7742,10 +7746,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7771,10 +7775,10 @@
         <v>432</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7825,7 +7829,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7837,7 +7841,7 @@
         <v>435</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7846,10 +7850,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7860,10 +7864,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7889,16 +7893,16 @@
         <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7926,10 +7930,10 @@
         <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7947,7 +7951,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7965,10 +7969,10 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>369</v>
@@ -7982,10 +7986,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8011,16 +8015,16 @@
         <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -8048,10 +8052,10 @@
         <v>270</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -8069,7 +8073,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8087,10 +8091,10 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>369</v>
@@ -8104,10 +8108,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8130,17 +8134,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -8189,7 +8193,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8213,7 +8217,7 @@
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -8224,10 +8228,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8253,10 +8257,10 @@
         <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8307,7 +8311,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8328,10 +8332,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -8342,10 +8346,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8368,16 +8372,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8427,7 +8431,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8448,10 +8452,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8462,10 +8466,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8488,16 +8492,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8547,7 +8551,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8568,10 +8572,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8582,10 +8586,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8593,10 +8597,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8611,16 +8615,16 @@
         <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8657,7 +8661,7 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8667,7 +8671,7 @@
         <v>314</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8688,10 +8692,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8702,10 +8706,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8820,10 +8824,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8940,10 +8944,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9062,10 +9066,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9091,13 +9095,13 @@
         <v>182</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>268</v>
@@ -9149,7 +9153,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -9167,7 +9171,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>275</v>
@@ -9184,10 +9188,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9213,13 +9217,13 @@
         <v>340</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>344</v>
@@ -9271,7 +9275,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9289,7 +9293,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>347</v>
@@ -9306,10 +9310,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9335,13 +9339,13 @@
         <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>354</v>
@@ -9393,7 +9397,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9428,10 +9432,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9515,7 +9519,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9550,10 +9554,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9579,10 +9583,10 @@
         <v>21</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>419</v>
@@ -9637,7 +9641,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9672,13 +9676,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>21</v>
@@ -9703,16 +9707,16 @@
         <v>416</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9761,7 +9765,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9782,10 +9786,10 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9796,10 +9800,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9914,10 +9918,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10034,10 +10038,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10156,10 +10160,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10185,13 +10189,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>268</v>
@@ -10204,7 +10208,7 @@
         <v>21</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>21</v>
@@ -10243,7 +10247,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>93</v>
@@ -10261,7 +10265,7 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>275</v>
@@ -10278,10 +10282,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10304,16 +10308,16 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>344</v>
@@ -10365,7 +10369,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10383,7 +10387,7 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>347</v>
@@ -10400,10 +10404,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10518,10 +10522,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10638,10 +10642,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10664,19 +10668,19 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10725,7 +10729,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10746,10 +10750,10 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>21</v>
@@ -10760,10 +10764,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10789,20 +10793,20 @@
         <v>113</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R70" t="s" s="2">
         <v>21</v>
@@ -10826,10 +10830,10 @@
         <v>176</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10847,7 +10851,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10868,10 +10872,10 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10882,10 +10886,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10911,14 +10915,14 @@
         <v>160</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10928,7 +10932,7 @@
         <v>21</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>21</v>
@@ -10967,7 +10971,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10988,10 +10992,10 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>21</v>
@@ -11002,10 +11006,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11031,14 +11035,14 @@
         <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -11048,7 +11052,7 @@
         <v>21</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>21</v>
@@ -11087,7 +11091,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11096,7 +11100,7 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -11108,10 +11112,10 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
@@ -11122,10 +11126,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11151,16 +11155,16 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11170,7 +11174,7 @@
         <v>21</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>21</v>
@@ -11209,7 +11213,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11230,10 +11234,10 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>21</v>
@@ -11244,10 +11248,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11273,13 +11277,13 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>354</v>
@@ -11331,7 +11335,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11366,10 +11370,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11453,7 +11457,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11488,10 +11492,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11517,10 +11521,10 @@
         <v>83</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>419</v>
@@ -11575,7 +11579,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11610,13 +11614,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
@@ -11641,16 +11645,16 @@
         <v>416</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11699,7 +11703,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11720,10 +11724,10 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
@@ -11734,10 +11738,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11852,10 +11856,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11972,10 +11976,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12094,10 +12098,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12123,13 +12127,13 @@
         <v>182</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>268</v>
@@ -12142,7 +12146,7 @@
         <v>21</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>21</v>
@@ -12181,7 +12185,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -12199,7 +12203,7 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>275</v>
@@ -12216,10 +12220,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12242,16 +12246,16 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>344</v>
@@ -12303,7 +12307,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12321,7 +12325,7 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>347</v>
@@ -12338,10 +12342,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12456,10 +12460,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12576,10 +12580,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12602,19 +12606,19 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12663,7 +12667,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12684,10 +12688,10 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>21</v>
@@ -12698,10 +12702,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12727,20 +12731,20 @@
         <v>113</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q86" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R86" t="s" s="2">
         <v>21</v>
@@ -12764,10 +12768,10 @@
         <v>176</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>21</v>
@@ -12785,7 +12789,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12806,10 +12810,10 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>21</v>
@@ -12820,10 +12824,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12849,14 +12853,14 @@
         <v>160</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -12866,7 +12870,7 @@
         <v>21</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>21</v>
@@ -12905,7 +12909,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12926,10 +12930,10 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>21</v>
@@ -12940,10 +12944,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12969,14 +12973,14 @@
         <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -12986,7 +12990,7 @@
         <v>21</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>21</v>
@@ -13025,7 +13029,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13034,7 +13038,7 @@
         <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>105</v>
@@ -13046,10 +13050,10 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>21</v>
@@ -13060,10 +13064,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13089,16 +13093,16 @@
         <v>113</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -13108,7 +13112,7 @@
         <v>21</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>21</v>
@@ -13147,7 +13151,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13168,10 +13172,10 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>21</v>
@@ -13182,10 +13186,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13211,13 +13215,13 @@
         <v>182</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>354</v>
@@ -13269,7 +13273,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13304,10 +13308,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13391,7 +13395,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13426,10 +13430,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13455,10 +13459,10 @@
         <v>83</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>419</v>
@@ -13513,7 +13517,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13548,13 +13552,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>21</v>
@@ -13579,16 +13583,16 @@
         <v>416</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13637,7 +13641,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13658,10 +13662,10 @@
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13672,10 +13676,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13790,10 +13794,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13910,10 +13914,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14032,10 +14036,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14061,13 +14065,13 @@
         <v>182</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O97" t="s" s="2">
         <v>268</v>
@@ -14080,7 +14084,7 @@
         <v>21</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>21</v>
@@ -14119,7 +14123,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>93</v>
@@ -14137,7 +14141,7 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>275</v>
@@ -14154,10 +14158,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14180,16 +14184,16 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O98" t="s" s="2">
         <v>344</v>
@@ -14241,7 +14245,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14259,7 +14263,7 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>347</v>
@@ -14276,10 +14280,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14394,10 +14398,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14514,10 +14518,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14540,19 +14544,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14601,7 +14605,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14622,10 +14626,10 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>21</v>
@@ -14636,10 +14640,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14665,20 +14669,20 @@
         <v>113</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R102" t="s" s="2">
         <v>21</v>
@@ -14702,10 +14706,10 @@
         <v>176</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14723,7 +14727,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14744,10 +14748,10 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>21</v>
@@ -14758,10 +14762,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14787,14 +14791,14 @@
         <v>160</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -14804,7 +14808,7 @@
         <v>21</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>21</v>
@@ -14843,7 +14847,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14864,10 +14868,10 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>21</v>
@@ -14878,10 +14882,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14907,14 +14911,14 @@
         <v>107</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -14924,7 +14928,7 @@
         <v>21</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>21</v>
@@ -14963,7 +14967,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14972,7 +14976,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -14984,10 +14988,10 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>21</v>
@@ -14998,10 +15002,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15027,16 +15031,16 @@
         <v>113</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -15046,7 +15050,7 @@
         <v>21</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>21</v>
@@ -15085,7 +15089,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15106,10 +15110,10 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>21</v>
@@ -15120,10 +15124,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15149,13 +15153,13 @@
         <v>182</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>354</v>
@@ -15207,7 +15211,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15242,10 +15246,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15329,7 +15333,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15364,10 +15368,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15393,10 +15397,10 @@
         <v>83</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>419</v>
@@ -15451,7 +15455,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15486,13 +15490,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>21</v>
@@ -15517,16 +15521,16 @@
         <v>416</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -15575,7 +15579,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15596,10 +15600,10 @@
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>21</v>
@@ -15610,10 +15614,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15728,10 +15732,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15848,10 +15852,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15970,10 +15974,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15999,13 +16003,13 @@
         <v>182</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O113" t="s" s="2">
         <v>268</v>
@@ -16018,7 +16022,7 @@
         <v>21</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>21</v>
@@ -16057,7 +16061,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>93</v>
@@ -16075,7 +16079,7 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>275</v>
@@ -16092,10 +16096,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16118,16 +16122,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>344</v>
@@ -16179,7 +16183,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16197,7 +16201,7 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>347</v>
@@ -16214,10 +16218,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16332,10 +16336,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16452,10 +16456,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16478,19 +16482,19 @@
         <v>94</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -16539,7 +16543,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16560,10 +16564,10 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>21</v>
@@ -16574,10 +16578,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16603,20 +16607,20 @@
         <v>113</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q118" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R118" t="s" s="2">
         <v>21</v>
@@ -16640,10 +16644,10 @@
         <v>176</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>21</v>
@@ -16661,7 +16665,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16682,10 +16686,10 @@
         <v>21</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>21</v>
@@ -16696,10 +16700,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16725,14 +16729,14 @@
         <v>160</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16742,7 +16746,7 @@
         <v>21</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>21</v>
@@ -16781,7 +16785,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16802,10 +16806,10 @@
         <v>21</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>21</v>
@@ -16816,10 +16820,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16845,14 +16849,14 @@
         <v>107</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>21</v>
@@ -16862,7 +16866,7 @@
         <v>21</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>21</v>
@@ -16901,7 +16905,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16910,7 +16914,7 @@
         <v>93</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>105</v>
@@ -16922,10 +16926,10 @@
         <v>21</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>21</v>
@@ -16936,10 +16940,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16965,16 +16969,16 @@
         <v>113</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>21</v>
@@ -16984,7 +16988,7 @@
         <v>21</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>21</v>
@@ -17023,7 +17027,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17044,10 +17048,10 @@
         <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>21</v>
@@ -17058,10 +17062,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17087,13 +17091,13 @@
         <v>182</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>354</v>
@@ -17145,7 +17149,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17180,10 +17184,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17267,7 +17271,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17302,10 +17306,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17331,10 +17335,10 @@
         <v>83</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>419</v>
@@ -17389,7 +17393,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17424,13 +17428,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>21</v>
@@ -17455,16 +17459,16 @@
         <v>416</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>21</v>
@@ -17513,7 +17517,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17534,10 +17538,10 @@
         <v>21</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>21</v>
@@ -17548,10 +17552,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17666,10 +17670,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17786,10 +17790,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17908,10 +17912,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17937,13 +17941,13 @@
         <v>182</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O129" t="s" s="2">
         <v>268</v>
@@ -17956,7 +17960,7 @@
         <v>21</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>21</v>
@@ -17995,7 +17999,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>93</v>
@@ -18013,7 +18017,7 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>275</v>
@@ -18030,10 +18034,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18056,16 +18060,16 @@
         <v>94</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O130" t="s" s="2">
         <v>344</v>
@@ -18117,7 +18121,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18135,7 +18139,7 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>347</v>
@@ -18152,10 +18156,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18270,10 +18274,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18390,10 +18394,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18416,19 +18420,19 @@
         <v>94</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>21</v>
@@ -18477,7 +18481,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -18498,10 +18502,10 @@
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>21</v>
@@ -18512,10 +18516,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18541,20 +18545,20 @@
         <v>113</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q134" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R134" t="s" s="2">
         <v>21</v>
@@ -18578,10 +18582,10 @@
         <v>176</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>21</v>
@@ -18599,7 +18603,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -18620,10 +18624,10 @@
         <v>21</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>21</v>
@@ -18634,10 +18638,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18663,14 +18667,14 @@
         <v>160</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -18680,7 +18684,7 @@
         <v>21</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>21</v>
@@ -18719,7 +18723,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -18740,10 +18744,10 @@
         <v>21</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>21</v>
@@ -18754,10 +18758,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18783,14 +18787,14 @@
         <v>107</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>21</v>
@@ -18800,7 +18804,7 @@
         <v>21</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>21</v>
@@ -18839,7 +18843,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -18848,7 +18852,7 @@
         <v>93</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>105</v>
@@ -18860,10 +18864,10 @@
         <v>21</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>21</v>
@@ -18874,10 +18878,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18903,16 +18907,16 @@
         <v>113</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>21</v>
@@ -18922,7 +18926,7 @@
         <v>21</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>21</v>
@@ -18961,7 +18965,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -18982,10 +18986,10 @@
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>21</v>
@@ -18996,10 +19000,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19025,13 +19029,13 @@
         <v>182</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O138" t="s" s="2">
         <v>354</v>
@@ -19083,7 +19087,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19118,10 +19122,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19205,7 +19209,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19240,10 +19244,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19269,10 +19273,10 @@
         <v>83</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>419</v>
@@ -19327,7 +19331,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
